--- a/光伏配储项目/电价数据/2026/紫峰站.xlsx
+++ b/光伏配储项目/电价数据/2026/紫峰站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.344</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8470700000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26485</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07748999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.15889</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.32932</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25655</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24584</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.98742</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.5522100000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5960800000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.76567</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.22516</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.65742</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44216</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.45005</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.68523</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9541000000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5345599999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.28826</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.40437</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.16483</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.22106</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.40261</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.52832</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.49276</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.75795</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.81552</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.28491</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.13276</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.93899</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.84065</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7997799999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.53659</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.50186</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.48468</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.44042</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.74188</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.92525</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.98781</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5096700000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5276900000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.51819</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51819</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49911</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47991</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.27232</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.47412</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.48482</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.49562</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.68152</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.64771</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.84736</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.32488</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.7124199999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6701900000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.94925</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.61934</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7905599999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8450299999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.24598</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.6855</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.20671</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.90287</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.30391</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.19088</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.37383</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.10748</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6955399999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.05411</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.93975</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05511</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9322</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.15384</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.94021</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45506</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.8972599999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9329299999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45407</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43231</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44833</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33532</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5200499999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49838</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50192</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45394</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48443</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44669</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.13808</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.09509999999999999</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.85322</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.69312</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.6801</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.86717</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.8631599999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.85749</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.8591799999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.52809</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.85673</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.86305</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.86966</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.01271</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.54775</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.60099</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.81138</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.81529</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.68992</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.72576</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5279700000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.82533</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44029</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45677</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52451</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.59758</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.6434299999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.64508</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.65871</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.31135</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6279400000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6988099999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47137</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50956</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6384</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.78483</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.77647</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.90377</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.46494</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6540900000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45217</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.53425</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6250800000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.80557</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.58192</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.92552</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.74336</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.62136</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.57059</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71149</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44205</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46131</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3428</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.53647</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5149</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39687</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46325</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39618</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44399</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.49638</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.63805</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.46792</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45996</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.72464</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38434</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6262300000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.53896</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.45392</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.41083</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49637</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.6609700000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5166000000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46932</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.49057</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.58387</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6874400000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.50619</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6585700000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.54315</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.51287</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50264</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.46707</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.44331</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42278</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3303</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02098</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.27736</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26401</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.25017</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.11677</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.08495999999999999</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44264</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42168</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31417</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.22233</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.23131</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.21882</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.17874</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.14329</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.23912</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.16336</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24084</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.20401</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.16077</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24106</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.18848</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10099</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04248</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009679999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20557</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04895</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20034</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.5091100000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05972</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05792</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31399</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.34413</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.4219</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43199</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46279</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78595</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8702300000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.64785</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.56997</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44304</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.55374</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60329</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.89828</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.58908</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.84501</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26275</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59975</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.44759</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28241</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.16711</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25808</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.25724</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27269</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25588</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28249</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32082</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9321699999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.51057</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.5214</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20744</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.1999</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.44436</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.28961</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8525199999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.53912</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.18521</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7049</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.81909</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6554800000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.20604</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.21093</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44644</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50113</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43031</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.27951</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.28384</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.47165</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.15697</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27364</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.41451</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25915</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14994</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02219</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.27776</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.28578</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.44348</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.56817</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.25909</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.24923</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.15132</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.17862</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.17434</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.17159</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.17172</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.14056</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.23153</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.25332</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.25092</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.14155</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.14096</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28636</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.17898</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.16884</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.1944</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.18008</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.16702</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.26681</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.23636</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.27063</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.14594</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.13961</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.19921</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.44853</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26597</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28542</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27223</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28614</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.28195</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.28553</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.29151</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24028</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27516</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29355</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.28888</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28082</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28525</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.49596</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.2804700000000001</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.27913</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30087</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.28842</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.28888</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.23821</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.72609</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5195599999999999</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48204</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45899</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5284099999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.44808</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.59557</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25371</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.75737</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.47126</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.45112</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.42796</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5820599999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.43513</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.46625</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.6703300000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48271</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.44008</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.49316</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44284</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7129</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.24113</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47844</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22292</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.26353</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.19358</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27864</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27293</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.18442</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.17723</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26894</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26894</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26895</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.26888</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.17888</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.17637</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.13702</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.22693</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25597</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.18193</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.20891</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.18786</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.14892</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.14103</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20226</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.22817</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27236</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25124</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.28154</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.24301</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.26516</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.27761</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.27314</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.27977</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22105</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.20215</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.15287</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22321</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31684</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27404</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.27924</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.26748</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.27757</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.26653</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27457</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.26882</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.27774</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.26837</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6481699999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.53553</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29205</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.40566</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41521</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.45303</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48716</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.68347</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6381100000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6872200000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84549</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.51566</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.46157</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.30978</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.26583</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.2824700000000001</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44409</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.41047</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.46203</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.5017699999999999</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5455599999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.56843</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42811</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67384</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.85253</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.56247</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.26797</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7739199999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61411</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.63966</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.30117</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28009</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.03913000000000001</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.45993</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41057</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.45243</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.41466</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.21295</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.2147</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.21021</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.23317</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.25989</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.22206</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.26661</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.16765</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.17947</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.17192</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.20493</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.17646</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.28888</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.25778</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.21586</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.20457</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.14862</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.04144</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25225</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.04272</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.04184</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.14889</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.18552</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.14765</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.13912</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.14323</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.14606</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.04078</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.14855</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.15851</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.16834</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.13224</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28048</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.26761</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.66944</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.26479</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00371</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.23896</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.2587</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28435</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.25349</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.25895</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.20388</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.22808</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.20751</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.23203</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.25603</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.15872</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.16559</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24678</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.14861</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27174</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.15005</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.22581</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.2195</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26624</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.17057</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.16779</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26212</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.04225</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19259</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21497</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20616</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.006730000000000001</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.03997999999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.0401</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.0401</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.04004</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18713</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.0401</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.0401</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.16394</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.03962</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.03175</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24195</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.00724</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.009470000000000001</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15342</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01453</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00204</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03647</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01337</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03553</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20608</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.03949</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26219</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.03332</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.26565</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26918</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.15249</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.14836</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15247</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15005</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.14636</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.13609</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.03836999999999999</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.03786</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.03711</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.17503</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26923</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.22123</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.24811</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85511</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08697000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.04055</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24208</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.6055700000000001</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00279</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06975000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47565</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.64838</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5277000000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.80383</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9933099999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.6275499999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.85376</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.85661</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.96165</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.42245</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30164</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25251</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.17298</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25098</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24481</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.2386</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.20382</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.23511</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.18913</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.15089</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.18493</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.14831</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.13772</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.16457</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.21736</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.25787</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22525</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23348</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24374</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25875</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28286</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28421</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5887100000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.44029</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.46794</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48304</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8484700000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.84484</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5519500000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.69204</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8965</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.57787</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19552</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31094</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.53507</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.54332</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.17346</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.86637</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.57629</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.75734</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.60472</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.44095</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.73133</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.67549</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.12055</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.87164</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7450800000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.60517</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31558</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42133</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.52961</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1978</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43464</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.43671</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.48788</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.43173</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5307000000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42834</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.45096</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47302</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.58199</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4921</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41832</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31913</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.72605</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46415</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43192</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41934</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26251</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.44575</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45853</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44748</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.46846</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.43627</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5305800000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.42824</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.42003</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33388</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14583</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19875</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14747</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04844</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14597</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18678</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22695</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17083</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20419</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16771</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.43804</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.55461</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.42357</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.44947</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.48941</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.46739</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36554</v>
       </c>
     </row>
   </sheetData>
